--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2025 artfynd.xlsx
+++ b/artfynd/A 30159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016976</v>
       </c>
       <c r="B2" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
